--- a/insurance_forms/005_home_insurance_claim_intake_form--insurance_forms.xlsx
+++ b/insurance_forms/005_home_insurance_claim_intake_form--insurance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Upload Document</t>
+          <t>Upload Document 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Upload Image</t>
+          <t>Upload Image 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Upload Video</t>
+          <t>Upload Video 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Upload Audio</t>
+          <t>Upload Audio 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'water_damage'}</t>
+          <t>water_damage</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Water Damage'}</t>
+          <t>Water Damage</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fire_damage'}</t>
+          <t>fire_damage</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fire Damage'}</t>
+          <t>Fire Damage</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'vandalism'}</t>
+          <t>vandalism</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Vandalism'}</t>
+          <t>Vandalism</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'theft'}</t>
+          <t>theft</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Theft'}</t>
+          <t>Theft</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
